--- a/Data/Timeoff/timeoff.xlsx
+++ b/Data/Timeoff/timeoff.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ESEM2026\Data\Timeoff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\SANER2027\Data\Timeoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799E06AD-556C-4E38-B570-E35E861F2C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C12A54-2415-4311-A7AC-34CBE3F84430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="230">
   <si>
     <t>1042-1043</t>
     <phoneticPr fontId="1"/>
@@ -899,6 +899,10 @@
   </si>
   <si>
     <t>changed_lines</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Other</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8432,6 +8436,9 @@
       <c r="P136" t="s">
         <v>221</v>
       </c>
+      <c r="Q136" t="s">
+        <v>224</v>
+      </c>
       <c r="Y136" t="s">
         <v>227</v>
       </c>
@@ -8593,6 +8600,9 @@
       <c r="S139" t="s">
         <v>221</v>
       </c>
+      <c r="T139" t="s">
+        <v>229</v>
+      </c>
       <c r="Y139">
         <v>1</v>
       </c>
@@ -8647,6 +8657,9 @@
       </c>
       <c r="S140" t="s">
         <v>222</v>
+      </c>
+      <c r="T140" t="s">
+        <v>224</v>
       </c>
       <c r="Y140" t="s">
         <v>227</v>
